--- a/精選債券基金_客戶屬性對照矩陣_V2_1.xlsx
+++ b/精選債券基金_客戶屬性對照矩陣_V2_1.xlsx
@@ -7,10 +7,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品對照矩陣" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="篩選說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ETF商品對照矩陣" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="篩選說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品對照矩陣'!$A$2:$R$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETF商品對照矩陣'!$A$2:$R$8</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -125,8 +127,29 @@
       <name val="微軟正黑體"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -216,8 +239,13 @@
         <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -284,6 +312,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
@@ -291,7 +325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -453,6 +487,35 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3070,6 +3133,699 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="43.6" customWidth="1" min="3" max="3"/>
+    <col width="15.1" customWidth="1" min="4" max="4"/>
+    <col width="18.8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14.5" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14.8" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t>凱基精選ETF × 客戶屬性 對照表 (2026.09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="60" t="inlineStr">
+        <is>
+          <t>商品代碼</t>
+        </is>
+      </c>
+      <c r="B2" s="60" t="inlineStr">
+        <is>
+          <t>商品類別</t>
+        </is>
+      </c>
+      <c r="C2" s="60" t="inlineStr">
+        <is>
+          <t>商品名稱</t>
+        </is>
+      </c>
+      <c r="D2" s="60" t="inlineStr">
+        <is>
+          <t>幣別</t>
+        </is>
+      </c>
+      <c r="E2" s="60" t="inlineStr">
+        <is>
+          <t>近一年報酬率</t>
+        </is>
+      </c>
+      <c r="F2" s="60" t="inlineStr">
+        <is>
+          <t>近三年報酬率</t>
+        </is>
+      </c>
+      <c r="G2" s="60" t="inlineStr">
+        <is>
+          <t>收盤價</t>
+        </is>
+      </c>
+      <c r="H2" s="60" t="inlineStr">
+        <is>
+          <t>票面/配息率</t>
+        </is>
+      </c>
+      <c r="I2" s="60" t="inlineStr">
+        <is>
+          <t>配息頻率</t>
+        </is>
+      </c>
+      <c r="J2" s="60" t="inlineStr">
+        <is>
+          <t>參考買進價(%)</t>
+        </is>
+      </c>
+      <c r="K2" s="60" t="inlineStr">
+        <is>
+          <t>到期日</t>
+        </is>
+      </c>
+      <c r="L2" s="60" t="inlineStr">
+        <is>
+          <t>首次贖回日</t>
+        </is>
+      </c>
+      <c r="M2" s="60" t="inlineStr">
+        <is>
+          <t>風險接受度</t>
+        </is>
+      </c>
+      <c r="N2" s="60" t="inlineStr">
+        <is>
+          <t>投資類型</t>
+        </is>
+      </c>
+      <c r="O2" s="60" t="inlineStr">
+        <is>
+          <t>現金流需求</t>
+        </is>
+      </c>
+      <c r="P2" s="60" t="inlineStr">
+        <is>
+          <t>適合資產總值</t>
+        </is>
+      </c>
+      <c r="Q2" s="60" t="inlineStr">
+        <is>
+          <t>進場方式(現金持有)</t>
+        </is>
+      </c>
+      <c r="R2" s="60" t="inlineStr">
+        <is>
+          <t>商品特色</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="61" t="inlineStr">
+        <is>
+          <t>009816</t>
+        </is>
+      </c>
+      <c r="B3" s="62" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C3" s="63" t="inlineStr">
+        <is>
+          <t>凱基台灣TOP50 ETF</t>
+        </is>
+      </c>
+      <c r="D3" s="61" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E3" s="64" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F3" s="64" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G3" s="61" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="H3" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="61" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
+      <c r="J3" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="65" t="inlineStr">
+        <is>
+          <t>積極</t>
+        </is>
+      </c>
+      <c r="N3" s="61" t="inlineStr">
+        <is>
+          <t>成長</t>
+        </is>
+      </c>
+      <c r="O3" s="61" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
+      <c r="P3" s="61" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="Q3" s="61" t="inlineStr">
+        <is>
+          <t>單筆/定期定額</t>
+        </is>
+      </c>
+      <c r="R3" s="63" t="inlineStr">
+        <is>
+          <t>凱基投信發行；追蹤特選臺灣TOP50指數，市值型；台灣首檔不配息ETF，成分股股利留在基金內部再投入；2026/1/22 成立，未滿一年無完整年度績效，報酬率為成立以來參考數字</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>00915</t>
+        </is>
+      </c>
+      <c r="B4" s="62" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>凱基優選高股息30 ETF</t>
+        </is>
+      </c>
+      <c r="D4" s="61" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E4" s="64" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F4" s="64" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G4" s="61" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="H4" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="61" t="inlineStr">
+        <is>
+          <t>季配</t>
+        </is>
+      </c>
+      <c r="J4" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="66" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="N4" s="61" t="inlineStr">
+        <is>
+          <t>收益</t>
+        </is>
+      </c>
+      <c r="O4" s="61" t="inlineStr">
+        <is>
+          <t>季配</t>
+        </is>
+      </c>
+      <c r="P4" s="61" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q4" s="61" t="inlineStr">
+        <is>
+          <t>單筆/定期定額</t>
+        </is>
+      </c>
+      <c r="R4" s="63" t="inlineStr">
+        <is>
+          <t>凱基投信發行；追蹤臺灣多因子優選高股息30指數，多因子高股息策略，市值型；季配息（2、5、8、11月）；2022/08成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="61" t="inlineStr">
+        <is>
+          <t>00926</t>
+        </is>
+      </c>
+      <c r="B5" s="62" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>凱基全球菁英55 ETF</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F5" s="64" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G5" s="61" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="H5" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="61" t="inlineStr">
+        <is>
+          <t>年配</t>
+        </is>
+      </c>
+      <c r="J5" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="65" t="inlineStr">
+        <is>
+          <t>積極</t>
+        </is>
+      </c>
+      <c r="N5" s="61" t="inlineStr">
+        <is>
+          <t>成長</t>
+        </is>
+      </c>
+      <c r="O5" s="61" t="inlineStr">
+        <is>
+          <t>年配</t>
+        </is>
+      </c>
+      <c r="P5" s="61" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="Q5" s="61" t="inlineStr">
+        <is>
+          <t>單筆/定期定額</t>
+        </is>
+      </c>
+      <c r="R5" s="63" t="inlineStr">
+        <is>
+          <t>凱基投信發行；追蹤彭博全球菁英55指數，聚焦全球科技與消費龍頭股，海外股票型；年配息（12月）；2023/05成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>00945B</t>
+        </is>
+      </c>
+      <c r="B6" s="62" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
+        <is>
+          <t>凱基美國非投等債 ETF</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E6" s="64" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="F6" s="64" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="G6" s="61" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="H6" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="61" t="inlineStr">
+        <is>
+          <t>月配</t>
+        </is>
+      </c>
+      <c r="J6" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" s="67" t="inlineStr">
+        <is>
+          <t>穩健</t>
+        </is>
+      </c>
+      <c r="N6" s="61" t="inlineStr">
+        <is>
+          <t>收益</t>
+        </is>
+      </c>
+      <c r="O6" s="61" t="inlineStr">
+        <is>
+          <t>月配</t>
+        </is>
+      </c>
+      <c r="P6" s="61" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="Q6" s="61" t="inlineStr">
+        <is>
+          <t>單筆/定期定額</t>
+        </is>
+      </c>
+      <c r="R6" s="63" t="inlineStr">
+        <is>
+          <t>凱基投信發行；追蹤彭博美國企業非投資等級1-5年Ba至B債券指數，月配息型；全台首檔月配美國非投等債ETF；2024/05掛牌，尚未滿三年，報酬率為參考數字</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="B7" s="62" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
+        <is>
+          <t>元大台灣50 ETF</t>
+        </is>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F7" s="64" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G7" s="61" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="H7" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="61" t="inlineStr">
+        <is>
+          <t>半年配</t>
+        </is>
+      </c>
+      <c r="J7" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="65" t="inlineStr">
+        <is>
+          <t>積極</t>
+        </is>
+      </c>
+      <c r="N7" s="61" t="inlineStr">
+        <is>
+          <t>成長</t>
+        </is>
+      </c>
+      <c r="O7" s="61" t="inlineStr">
+        <is>
+          <t>半年配</t>
+        </is>
+      </c>
+      <c r="P7" s="61" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="Q7" s="61" t="inlineStr">
+        <is>
+          <t>單筆/定期定額</t>
+        </is>
+      </c>
+      <c r="R7" s="63" t="inlineStr">
+        <is>
+          <t>元大投信發行；追蹤台灣50指數，市值型；台灣規模最大、歷史最悠久的ETF之一，2003年成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="61" t="inlineStr">
+        <is>
+          <t>006208</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C8" s="63" t="inlineStr">
+        <is>
+          <t>富邦台50 ETF</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="E8" s="64" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F8" s="64" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G8" s="61" t="n">
+        <v>247.25</v>
+      </c>
+      <c r="H8" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="61" t="inlineStr">
+        <is>
+          <t>半年配</t>
+        </is>
+      </c>
+      <c r="J8" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="65" t="inlineStr">
+        <is>
+          <t>積極</t>
+        </is>
+      </c>
+      <c r="N8" s="61" t="inlineStr">
+        <is>
+          <t>成長</t>
+        </is>
+      </c>
+      <c r="O8" s="61" t="inlineStr">
+        <is>
+          <t>半年配</t>
+        </is>
+      </c>
+      <c r="P8" s="61" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="Q8" s="61" t="inlineStr">
+        <is>
+          <t>單筆/定期定額</t>
+        </is>
+      </c>
+      <c r="R8" s="63" t="inlineStr">
+        <is>
+          <t>富邦投信發行；追蹤台灣50指數，市值型；內扣費用率同類型中相對較低</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>資料來源與注意事項：</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="69" t="inlineStr">
+        <is>
+          <t>• 本表商品資料對應 js/catalog.js 的 ETF_PICKS 常數（js/flow.js showETFPicks() 專用的ETF精選清單，獨立於商品對照矩陣的問卷推薦清單之外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="69" t="inlineStr">
+        <is>
+          <t>• 00915／00926／00945B 為 2026.09.11 新增；近一年/近三年報酬率、收盤價為當日網路查證之參考數字（非即時官方數據），正式上線前需業務或商品負責人以官方淨值/報價覆核</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="69" t="inlineStr">
+        <is>
+          <t>• 009816 為 2026/1/22 成立之新基金，00945B 為 2024/05 掛牌，兩者皆未滿一整年/三年，報酬率為成立以來之參考數字，非真正年化報酬率</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="69" t="inlineStr">
+        <is>
+          <t>• 「票面/配息率」「參考買進價(%)」「到期日」「首次贖回日」為債券專用欄位，ETF 不適用，一律標示「-」</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:R8"/>
+  <mergeCells count="6">
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A13:R13"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A12:R12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
